--- a/pds_admin_karnataka/Backend/Backend/Data_1.xlsx
+++ b/pds_admin_karnataka/Backend/Backend/Data_1.xlsx
@@ -781,10 +781,10 @@
         <v>60</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
@@ -816,7 +816,7 @@
         <v>60</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>46.46</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>60</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>75.34</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>61</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>110.89</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>62</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>55.51</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -956,7 +956,7 @@
         <v>63</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>37.54</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>64</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>27.24</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>65</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>58.13</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>66</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>38.08</v>
       </c>
       <c r="I10">
         <v>0</v>
